--- a/2026年上半年减肥记录每一天.xlsx
+++ b/2026年上半年减肥记录每一天.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="22">
   <si>
     <t>时间</t>
   </si>
@@ -89,19 +89,13 @@
     <t>白菜 + 荞麦面 + 鸡蛋2</t>
   </si>
   <si>
-    <t>白馒头1 + 鸡蛋2 + 西红柿2</t>
+    <t>西红柿1</t>
   </si>
   <si>
-    <t>鸡蛋2</t>
+    <t>一般，缺少蛋白质和主食</t>
   </si>
   <si>
-    <t>白馒头1</t>
-  </si>
-  <si>
-    <t>西红柿2</t>
-  </si>
-  <si>
-    <t>目前82.5kg
+    <t>目前84.1kg
 本周争取到82.5kg</t>
   </si>
 </sst>
@@ -1157,7 +1151,7 @@
     </row>
     <row r="5" spans="1:8">
       <c r="A5" s="3">
-        <v>46031</v>
+        <v>46084</v>
       </c>
       <c r="B5" s="4" t="s">
         <v>8</v>
@@ -1165,20 +1159,16 @@
       <c r="C5" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="D5" s="4" t="s">
+      <c r="D5" s="4"/>
+      <c r="E5" s="4"/>
+      <c r="F5" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="G5" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="E5" s="4" t="s">
+      <c r="H5" s="5" t="s">
         <v>21</v>
-      </c>
-      <c r="F5" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="G5" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="H5" s="5" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -1186,7 +1176,9 @@
       <c r="B6" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="C6" s="4"/>
+      <c r="C6" s="4" t="s">
+        <v>16</v>
+      </c>
       <c r="D6" s="4"/>
       <c r="E6" s="4"/>
       <c r="F6" s="4"/>

--- a/2026年上半年减肥记录每一天.xlsx
+++ b/2026年上半年减肥记录每一天.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="32">
   <si>
     <t>时间</t>
   </si>
@@ -97,6 +97,39 @@
   <si>
     <t>目前84.1kg
 本周争取到82.5kg</t>
+  </si>
+  <si>
+    <t>荞麦面 + 白菜菠菜 + 鸡蛋</t>
+  </si>
+  <si>
+    <t>鸡蛋2</t>
+  </si>
+  <si>
+    <t>白菜菠菜</t>
+  </si>
+  <si>
+    <t>目前86.4kg
+本周争取到84.4kg</t>
+  </si>
+  <si>
+    <t>食野减脂餐</t>
+  </si>
+  <si>
+    <t>鸡腿肉</t>
+  </si>
+  <si>
+    <t>荞麦面 + 白菜少量芹菜 + 鸡蛋</t>
+  </si>
+  <si>
+    <t>目前85.65kg
+本周争取到84.4kg</t>
+  </si>
+  <si>
+    <t>鸡蛋 + 西红柿 + 玉米</t>
+  </si>
+  <si>
+    <t>2026-5-9
+(本周结束)</t>
   </si>
 </sst>
 </file>
@@ -725,7 +758,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -742,6 +775,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1198,49 +1234,105 @@
       <c r="H7" s="4"/>
     </row>
     <row r="8" spans="1:8">
-      <c r="A8" s="3"/>
-      <c r="B8" s="4"/>
-      <c r="C8" s="4"/>
-      <c r="D8" s="4"/>
-      <c r="E8" s="4"/>
-      <c r="F8" s="4"/>
-      <c r="G8" s="4"/>
-      <c r="H8" s="4"/>
+      <c r="A8" s="3">
+        <v>46148</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="D8" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="E8" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="F8" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="G8" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="H8" s="5" t="s">
+        <v>25</v>
+      </c>
     </row>
     <row r="9" spans="1:8">
-      <c r="A9" s="4"/>
-      <c r="B9" s="4"/>
-      <c r="C9" s="4"/>
-      <c r="D9" s="4"/>
+      <c r="A9" s="3"/>
+      <c r="B9" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="C9" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="D9" s="4" t="s">
+        <v>27</v>
+      </c>
       <c r="E9" s="4"/>
       <c r="F9" s="4"/>
-      <c r="G9" s="4"/>
+      <c r="G9" s="4" t="s">
+        <v>13</v>
+      </c>
       <c r="H9" s="4"/>
     </row>
     <row r="10" spans="1:8">
-      <c r="A10" s="4"/>
-      <c r="B10" s="4"/>
-      <c r="C10" s="4"/>
-      <c r="D10" s="4"/>
-      <c r="E10" s="4"/>
-      <c r="F10" s="4"/>
-      <c r="G10" s="4"/>
+      <c r="A10" s="3"/>
+      <c r="B10" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="C10" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="D10" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="E10" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="F10" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="G10" s="4" t="s">
+        <v>13</v>
+      </c>
       <c r="H10" s="4"/>
     </row>
     <row r="11" spans="1:8">
-      <c r="A11" s="3"/>
-      <c r="B11" s="4"/>
-      <c r="C11" s="4"/>
-      <c r="D11" s="4"/>
-      <c r="E11" s="4"/>
-      <c r="F11" s="4"/>
-      <c r="G11" s="4"/>
-      <c r="H11" s="5"/>
+      <c r="A11" s="3">
+        <v>46149</v>
+      </c>
+      <c r="B11" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="C11" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="D11" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="E11" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="F11" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="G11" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="H11" s="5" t="s">
+        <v>29</v>
+      </c>
     </row>
     <row r="12" spans="1:8">
-      <c r="A12" s="4"/>
-      <c r="B12" s="4"/>
-      <c r="C12" s="4"/>
+      <c r="A12" s="3"/>
+      <c r="B12" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="C12" s="4" t="s">
+        <v>30</v>
+      </c>
       <c r="D12" s="4"/>
       <c r="E12" s="4"/>
       <c r="F12" s="4"/>
@@ -1248,8 +1340,10 @@
       <c r="H12" s="4"/>
     </row>
     <row r="13" spans="1:8">
-      <c r="A13" s="4"/>
-      <c r="B13" s="4"/>
+      <c r="A13" s="3"/>
+      <c r="B13" s="4" t="s">
+        <v>17</v>
+      </c>
       <c r="C13" s="4"/>
       <c r="D13" s="4"/>
       <c r="E13" s="4"/>
@@ -1258,18 +1352,24 @@
       <c r="H13" s="4"/>
     </row>
     <row r="14" spans="1:8">
-      <c r="A14" s="3"/>
-      <c r="B14" s="4"/>
+      <c r="A14" s="3">
+        <v>46150</v>
+      </c>
+      <c r="B14" s="4" t="s">
+        <v>8</v>
+      </c>
       <c r="C14" s="4"/>
       <c r="D14" s="4"/>
       <c r="E14" s="4"/>
       <c r="F14" s="4"/>
       <c r="G14" s="4"/>
-      <c r="H14" s="4"/>
+      <c r="H14" s="5"/>
     </row>
     <row r="15" spans="1:8">
-      <c r="A15" s="4"/>
-      <c r="B15" s="4"/>
+      <c r="A15" s="3"/>
+      <c r="B15" s="4" t="s">
+        <v>15</v>
+      </c>
       <c r="C15" s="4"/>
       <c r="D15" s="4"/>
       <c r="E15" s="4"/>
@@ -1278,26 +1378,36 @@
       <c r="H15" s="4"/>
     </row>
     <row r="16" spans="1:8">
-      <c r="A16" s="4"/>
-      <c r="B16" s="4"/>
+      <c r="A16" s="3"/>
+      <c r="B16" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="C16" s="4"/>
       <c r="D16" s="4"/>
       <c r="E16" s="4"/>
+      <c r="F16" s="4"/>
       <c r="G16" s="4"/>
       <c r="H16" s="4"/>
     </row>
     <row r="17" spans="1:8">
-      <c r="A17" s="3"/>
-      <c r="B17" s="4"/>
+      <c r="A17" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="B17" s="4" t="s">
+        <v>8</v>
+      </c>
       <c r="C17" s="4"/>
       <c r="D17" s="4"/>
       <c r="E17" s="4"/>
       <c r="F17" s="4"/>
       <c r="G17" s="4"/>
-      <c r="H17" s="4"/>
+      <c r="H17" s="5"/>
     </row>
     <row r="18" spans="1:8">
-      <c r="A18" s="4"/>
-      <c r="B18" s="4"/>
+      <c r="A18" s="3"/>
+      <c r="B18" s="4" t="s">
+        <v>15</v>
+      </c>
       <c r="C18" s="4"/>
       <c r="D18" s="4"/>
       <c r="E18" s="4"/>
@@ -1306,8 +1416,11 @@
       <c r="H18" s="4"/>
     </row>
     <row r="19" spans="1:8">
-      <c r="A19" s="4"/>
-      <c r="B19" s="4"/>
+      <c r="A19" s="3"/>
+      <c r="B19" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="C19" s="4"/>
       <c r="D19" s="4"/>
       <c r="E19" s="4"/>
       <c r="F19" s="4"/>

--- a/2026年上半年减肥记录每一天.xlsx
+++ b/2026年上半年减肥记录每一天.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12255"/>
+    <workbookView windowWidth="31545" windowHeight="17655"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="35">
   <si>
     <t>时间</t>
   </si>
@@ -126,6 +126,15 @@
   </si>
   <si>
     <t>鸡蛋 + 西红柿 + 玉米</t>
+  </si>
+  <si>
+    <t>鸡蛋2 + 西红柿1 + 杂粮馒头1</t>
+  </si>
+  <si>
+    <t>杂粮馒头1</t>
+  </si>
+  <si>
+    <t>比较满意，多喝一个酸奶</t>
   </si>
   <si>
     <t>2026-5-9
@@ -1353,17 +1362,29 @@
     </row>
     <row r="14" spans="1:8">
       <c r="A14" s="3">
-        <v>46150</v>
+        <v>46167</v>
       </c>
       <c r="B14" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="C14" s="4"/>
-      <c r="D14" s="4"/>
-      <c r="E14" s="4"/>
-      <c r="F14" s="4"/>
-      <c r="G14" s="4"/>
-      <c r="H14" s="5"/>
+      <c r="C14" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="D14" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="E14" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="F14" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="G14" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="H14" s="5" t="s">
+        <v>29</v>
+      </c>
     </row>
     <row r="15" spans="1:8">
       <c r="A15" s="3"/>
@@ -1391,7 +1412,7 @@
     </row>
     <row r="17" spans="1:8">
       <c r="A17" s="6" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="B17" s="4" t="s">
         <v>8</v>

--- a/2026年上半年减肥记录每一天.xlsx
+++ b/2026年上半年减肥记录每一天.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="40">
   <si>
     <t>时间</t>
   </si>
@@ -137,8 +137,25 @@
     <t>比较满意，多喝一个酸奶</t>
   </si>
   <si>
-    <t>2026-5-9
-(本周结束)</t>
+    <t>2026-6-29
+(周一)</t>
+  </si>
+  <si>
+    <t>鸡蛋2 + 西红柿1 + 2/3玉米</t>
+  </si>
+  <si>
+    <t>2/3玉米</t>
+  </si>
+  <si>
+    <t>很满意，继续加油</t>
+  </si>
+  <si>
+    <t>目前82.0kg
+本周争取到79.5kg</t>
+  </si>
+  <si>
+    <t>目前81.5kg
+本周争取到79.5kg</t>
   </si>
 </sst>
 </file>
@@ -1417,19 +1434,33 @@
       <c r="B17" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="C17" s="4"/>
-      <c r="D17" s="4"/>
-      <c r="E17" s="4"/>
-      <c r="F17" s="4"/>
-      <c r="G17" s="4"/>
-      <c r="H17" s="5"/>
+      <c r="C17" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="D17" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="E17" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="F17" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="G17" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="H17" s="5" t="s">
+        <v>38</v>
+      </c>
     </row>
     <row r="18" spans="1:8">
       <c r="A18" s="3"/>
       <c r="B18" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="C18" s="4"/>
+      <c r="C18" s="4" t="s">
+        <v>16</v>
+      </c>
       <c r="D18" s="4"/>
       <c r="E18" s="4"/>
       <c r="F18" s="4"/>
@@ -1449,18 +1480,26 @@
       <c r="H19" s="4"/>
     </row>
     <row r="20" spans="1:8">
-      <c r="A20" s="3"/>
-      <c r="B20" s="4"/>
+      <c r="A20" s="6">
+        <v>46203</v>
+      </c>
+      <c r="B20" s="4" t="s">
+        <v>8</v>
+      </c>
       <c r="C20" s="4"/>
       <c r="D20" s="4"/>
       <c r="E20" s="4"/>
       <c r="F20" s="4"/>
-      <c r="G20" s="5"/>
-      <c r="H20" s="4"/>
+      <c r="G20" s="4"/>
+      <c r="H20" s="5" t="s">
+        <v>39</v>
+      </c>
     </row>
     <row r="21" spans="1:8">
-      <c r="A21" s="4"/>
-      <c r="B21" s="4"/>
+      <c r="A21" s="3"/>
+      <c r="B21" s="4" t="s">
+        <v>15</v>
+      </c>
       <c r="C21" s="4"/>
       <c r="D21" s="4"/>
       <c r="E21" s="4"/>
@@ -1469,18 +1508,24 @@
       <c r="H21" s="4"/>
     </row>
     <row r="22" spans="1:8">
-      <c r="A22" s="4"/>
-      <c r="B22" s="4"/>
-      <c r="C22" s="5"/>
+      <c r="A22" s="3"/>
+      <c r="B22" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="C22" s="4"/>
       <c r="D22" s="4"/>
       <c r="E22" s="4"/>
       <c r="F22" s="4"/>
-      <c r="G22" s="5"/>
+      <c r="G22" s="4"/>
       <c r="H22" s="4"/>
     </row>
     <row r="23" spans="1:8">
-      <c r="A23" s="3"/>
-      <c r="B23" s="4"/>
+      <c r="A23" s="6">
+        <v>46204</v>
+      </c>
+      <c r="B23" s="4" t="s">
+        <v>8</v>
+      </c>
       <c r="C23" s="4"/>
       <c r="D23" s="4"/>
       <c r="E23" s="4"/>
@@ -1489,8 +1534,10 @@
       <c r="H23" s="4"/>
     </row>
     <row r="24" spans="1:8">
-      <c r="A24" s="4"/>
-      <c r="B24" s="4"/>
+      <c r="A24" s="3"/>
+      <c r="B24" s="4" t="s">
+        <v>15</v>
+      </c>
       <c r="C24" s="4"/>
       <c r="D24" s="4"/>
       <c r="E24" s="4"/>
@@ -1499,8 +1546,10 @@
       <c r="H24" s="4"/>
     </row>
     <row r="25" spans="1:8">
-      <c r="A25" s="4"/>
-      <c r="B25" s="4"/>
+      <c r="A25" s="3"/>
+      <c r="B25" s="4" t="s">
+        <v>17</v>
+      </c>
       <c r="C25" s="4"/>
       <c r="D25" s="4"/>
       <c r="E25" s="4"/>
@@ -1509,8 +1558,12 @@
       <c r="H25" s="4"/>
     </row>
     <row r="26" spans="1:8">
-      <c r="A26" s="4"/>
-      <c r="B26" s="4"/>
+      <c r="A26" s="6">
+        <v>46205</v>
+      </c>
+      <c r="B26" s="4" t="s">
+        <v>8</v>
+      </c>
       <c r="C26" s="4"/>
       <c r="D26" s="4"/>
       <c r="E26" s="4"/>
@@ -1519,8 +1572,10 @@
       <c r="H26" s="4"/>
     </row>
     <row r="27" spans="1:8">
-      <c r="A27" s="4"/>
-      <c r="B27" s="4"/>
+      <c r="A27" s="3"/>
+      <c r="B27" s="4" t="s">
+        <v>15</v>
+      </c>
       <c r="C27" s="4"/>
       <c r="D27" s="4"/>
       <c r="E27" s="4"/>
@@ -1529,8 +1584,10 @@
       <c r="H27" s="4"/>
     </row>
     <row r="28" spans="1:8">
-      <c r="A28" s="4"/>
-      <c r="B28" s="4"/>
+      <c r="A28" s="3"/>
+      <c r="B28" s="4" t="s">
+        <v>17</v>
+      </c>
       <c r="C28" s="4"/>
       <c r="D28" s="4"/>
       <c r="E28" s="4"/>
@@ -1539,18 +1596,20 @@
       <c r="H28" s="4"/>
     </row>
     <row r="29" spans="1:8">
-      <c r="A29" s="4"/>
-      <c r="B29" s="4"/>
-      <c r="C29" s="4"/>
-      <c r="D29" s="4"/>
-      <c r="E29" s="4"/>
-      <c r="F29" s="4"/>
+      <c r="A29" s="6">
+        <v>46206</v>
+      </c>
+      <c r="B29" s="4" t="s">
+        <v>8</v>
+      </c>
       <c r="G29" s="4"/>
       <c r="H29" s="4"/>
     </row>
     <row r="30" spans="1:8">
-      <c r="A30" s="4"/>
-      <c r="B30" s="4"/>
+      <c r="A30" s="3"/>
+      <c r="B30" s="4" t="s">
+        <v>15</v>
+      </c>
       <c r="C30" s="4"/>
       <c r="D30" s="4"/>
       <c r="E30" s="4"/>
@@ -1559,8 +1618,10 @@
       <c r="H30" s="4"/>
     </row>
     <row r="31" spans="1:8">
-      <c r="A31" s="4"/>
-      <c r="B31" s="4"/>
+      <c r="A31" s="3"/>
+      <c r="B31" s="4" t="s">
+        <v>17</v>
+      </c>
       <c r="C31" s="4"/>
       <c r="D31" s="4"/>
       <c r="E31" s="4"/>

--- a/2026年上半年减肥记录每一天.xlsx
+++ b/2026年上半年减肥记录每一天.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="56">
   <si>
     <t>时间</t>
   </si>
@@ -154,7 +154,56 @@
 本周争取到79.5kg</t>
   </si>
   <si>
-    <t>目前81.5kg
+    <t>鸡蛋黄瓜馒头 + 油麦菜</t>
+  </si>
+  <si>
+    <t>鸡蛋1</t>
+  </si>
+  <si>
+    <t>馒头1</t>
+  </si>
+  <si>
+    <t>黄瓜 + 油麦菜</t>
+  </si>
+  <si>
+    <t>比较满意，继续加油</t>
+  </si>
+  <si>
+    <t>鸡蛋2 + 西红柿2 + 1/2玉米</t>
+  </si>
+  <si>
+    <t>1/2玉米</t>
+  </si>
+  <si>
+    <t>西红柿2</t>
+  </si>
+  <si>
+    <t>很满意</t>
+  </si>
+  <si>
+    <t>目前81.4kg
+本周争取到79.5kg</t>
+  </si>
+  <si>
+    <t>猪脚饭</t>
+  </si>
+  <si>
+    <t>比较满意，只吃几口米饭</t>
+  </si>
+  <si>
+    <t>大蓉和</t>
+  </si>
+  <si>
+    <t>正常有应酬</t>
+  </si>
+  <si>
+    <t>没吃</t>
+  </si>
+  <si>
+    <t>昨天应酬，空一顿消消食</t>
+  </si>
+  <si>
+    <t>目前82.3kg
 本周争取到79.5kg</t>
   </si>
 </sst>
@@ -1472,11 +1521,21 @@
       <c r="B19" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="C19" s="4"/>
-      <c r="D19" s="4"/>
-      <c r="E19" s="4"/>
-      <c r="F19" s="4"/>
-      <c r="G19" s="4"/>
+      <c r="C19" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="D19" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="E19" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="F19" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="G19" s="4" t="s">
+        <v>43</v>
+      </c>
       <c r="H19" s="4"/>
     </row>
     <row r="20" spans="1:8">
@@ -1486,13 +1545,23 @@
       <c r="B20" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="C20" s="4"/>
-      <c r="D20" s="4"/>
-      <c r="E20" s="4"/>
-      <c r="F20" s="4"/>
-      <c r="G20" s="4"/>
+      <c r="C20" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="D20" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="E20" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="F20" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="G20" s="4" t="s">
+        <v>47</v>
+      </c>
       <c r="H20" s="5" t="s">
-        <v>39</v>
+        <v>48</v>
       </c>
     </row>
     <row r="21" spans="1:8">
@@ -1500,11 +1569,15 @@
       <c r="B21" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="C21" s="4"/>
+      <c r="C21" s="4" t="s">
+        <v>49</v>
+      </c>
       <c r="D21" s="4"/>
       <c r="E21" s="4"/>
       <c r="F21" s="4"/>
-      <c r="G21" s="4"/>
+      <c r="G21" s="4" t="s">
+        <v>50</v>
+      </c>
       <c r="H21" s="4"/>
     </row>
     <row r="22" spans="1:8">
@@ -1512,11 +1585,15 @@
       <c r="B22" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="C22" s="4"/>
+      <c r="C22" s="4" t="s">
+        <v>51</v>
+      </c>
       <c r="D22" s="4"/>
       <c r="E22" s="4"/>
       <c r="F22" s="4"/>
-      <c r="G22" s="4"/>
+      <c r="G22" s="4" t="s">
+        <v>52</v>
+      </c>
       <c r="H22" s="4"/>
     </row>
     <row r="23" spans="1:8">
@@ -1526,12 +1603,18 @@
       <c r="B23" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="C23" s="4"/>
+      <c r="C23" s="4" t="s">
+        <v>53</v>
+      </c>
       <c r="D23" s="4"/>
       <c r="E23" s="4"/>
       <c r="F23" s="4"/>
-      <c r="G23" s="4"/>
-      <c r="H23" s="4"/>
+      <c r="G23" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="H23" s="5" t="s">
+        <v>55</v>
+      </c>
     </row>
     <row r="24" spans="1:8">
       <c r="A24" s="3"/>

--- a/2026年上半年减肥记录每一天.xlsx
+++ b/2026年上半年减肥记录每一天.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="68">
   <si>
     <t>时间</t>
   </si>
@@ -205,6 +205,43 @@
   <si>
     <t>目前82.3kg
 本周争取到79.5kg</t>
+  </si>
+  <si>
+    <t>subway地下铁</t>
+  </si>
+  <si>
+    <t>牛肉</t>
+  </si>
+  <si>
+    <t>全麦面包</t>
+  </si>
+  <si>
+    <t>黄瓜 + 西红柿</t>
+  </si>
+  <si>
+    <t>满意，吃饱了</t>
+  </si>
+  <si>
+    <t>火腿肠 + 青椒 + 圆葱</t>
+  </si>
+  <si>
+    <t>西兰花 + 鸡蛋 + 虾仁 + 一点米饭</t>
+  </si>
+  <si>
+    <t>鸡蛋 + 虾仁</t>
+  </si>
+  <si>
+    <t>一点米饭</t>
+  </si>
+  <si>
+    <t>西兰花</t>
+  </si>
+  <si>
+    <t>比较满意，注释偏少</t>
+  </si>
+  <si>
+    <t>目前82.3kg
+本周争取到80.0kg</t>
   </si>
 </sst>
 </file>
@@ -1621,11 +1658,21 @@
       <c r="B24" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="C24" s="4"/>
-      <c r="D24" s="4"/>
-      <c r="E24" s="4"/>
-      <c r="F24" s="4"/>
-      <c r="G24" s="4"/>
+      <c r="C24" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="D24" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="E24" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="F24" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="G24" s="4" t="s">
+        <v>60</v>
+      </c>
       <c r="H24" s="4"/>
     </row>
     <row r="25" spans="1:8">
@@ -1633,7 +1680,9 @@
       <c r="B25" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="C25" s="4"/>
+      <c r="C25" s="4" t="s">
+        <v>61</v>
+      </c>
       <c r="D25" s="4"/>
       <c r="E25" s="4"/>
       <c r="F25" s="4"/>
@@ -1647,12 +1696,24 @@
       <c r="B26" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="C26" s="4"/>
-      <c r="D26" s="4"/>
-      <c r="E26" s="4"/>
-      <c r="F26" s="4"/>
-      <c r="G26" s="4"/>
-      <c r="H26" s="4"/>
+      <c r="C26" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="D26" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="E26" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="F26" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="G26" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="H26" s="5" t="s">
+        <v>67</v>
+      </c>
     </row>
     <row r="27" spans="1:8">
       <c r="A27" s="3"/>

--- a/2026年上半年减肥记录每一天.xlsx
+++ b/2026年上半年减肥记录每一天.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="122" uniqueCount="73">
   <si>
     <t>时间</t>
   </si>
@@ -242,6 +242,21 @@
   <si>
     <t>目前82.3kg
 本周争取到80.0kg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">乌鸡米线 + 拍黄瓜 + 海带三丝 + 豆汤饭 </t>
+  </si>
+  <si>
+    <t>荤素搭配</t>
+  </si>
+  <si>
+    <t>凯里酸汤火锅</t>
+  </si>
+  <si>
+    <t>还行</t>
+  </si>
+  <si>
+    <t>半个馒头 + 西红柿鸡蛋</t>
   </si>
 </sst>
 </file>
@@ -870,7 +885,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -891,6 +906,9 @@
     </xf>
     <xf numFmtId="14" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -1720,11 +1738,15 @@
       <c r="B27" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="C27" s="4"/>
+      <c r="C27" s="4" t="s">
+        <v>68</v>
+      </c>
       <c r="D27" s="4"/>
       <c r="E27" s="4"/>
       <c r="F27" s="4"/>
-      <c r="G27" s="4"/>
+      <c r="G27" s="4" t="s">
+        <v>69</v>
+      </c>
       <c r="H27" s="4"/>
     </row>
     <row r="28" spans="1:8">
@@ -1732,11 +1754,15 @@
       <c r="B28" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="C28" s="4"/>
+      <c r="C28" s="4" t="s">
+        <v>70</v>
+      </c>
       <c r="D28" s="4"/>
       <c r="E28" s="4"/>
       <c r="F28" s="4"/>
-      <c r="G28" s="4"/>
+      <c r="G28" s="4" t="s">
+        <v>71</v>
+      </c>
       <c r="H28" s="4"/>
     </row>
     <row r="29" spans="1:8">
@@ -1746,8 +1772,13 @@
       <c r="B29" s="4" t="s">
         <v>8</v>
       </c>
+      <c r="C29" s="7" t="s">
+        <v>72</v>
+      </c>
       <c r="G29" s="4"/>
-      <c r="H29" s="4"/>
+      <c r="H29" s="5" t="s">
+        <v>67</v>
+      </c>
     </row>
     <row r="30" spans="1:8">
       <c r="A30" s="3"/>

--- a/2026年上半年减肥记录每一天.xlsx
+++ b/2026年上半年减肥记录每一天.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="122" uniqueCount="73">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="76">
   <si>
     <t>时间</t>
   </si>
@@ -257,6 +257,16 @@
   </si>
   <si>
     <t>半个馒头 + 西红柿鸡蛋</t>
+  </si>
+  <si>
+    <t>一个包子</t>
+  </si>
+  <si>
+    <t>有点少，中午要吃的素点</t>
+  </si>
+  <si>
+    <t>目前82.9kg
+本周争取到81.0kg</t>
   </si>
 </sst>
 </file>
@@ -885,7 +895,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -906,9 +916,6 @@
     </xf>
     <xf numFmtId="14" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -1772,7 +1779,7 @@
       <c r="B29" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="C29" s="7" t="s">
+      <c r="C29" s="4" t="s">
         <v>72</v>
       </c>
       <c r="G29" s="4"/>
@@ -1805,18 +1812,30 @@
       <c r="H31" s="4"/>
     </row>
     <row r="32" spans="1:8">
-      <c r="A32" s="3"/>
-      <c r="B32" s="4"/>
-      <c r="C32" s="4"/>
-      <c r="D32" s="4"/>
-      <c r="E32" s="4"/>
-      <c r="F32" s="4"/>
-      <c r="G32" s="4"/>
-      <c r="H32" s="5"/>
+      <c r="A32" s="6">
+        <v>46209</v>
+      </c>
+      <c r="B32" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="C32" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="D32" s="1"/>
+      <c r="E32" s="1"/>
+      <c r="F32" s="1"/>
+      <c r="G32" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="H32" s="5" t="s">
+        <v>75</v>
+      </c>
     </row>
     <row r="33" spans="1:8">
-      <c r="A33" s="4"/>
-      <c r="B33" s="4"/>
+      <c r="A33" s="3"/>
+      <c r="B33" s="4" t="s">
+        <v>15</v>
+      </c>
       <c r="C33" s="4"/>
       <c r="D33" s="4"/>
       <c r="E33" s="4"/>
@@ -1825,8 +1844,10 @@
       <c r="H33" s="4"/>
     </row>
     <row r="34" spans="1:8">
-      <c r="A34" s="4"/>
-      <c r="B34" s="4"/>
+      <c r="A34" s="3"/>
+      <c r="B34" s="4" t="s">
+        <v>17</v>
+      </c>
       <c r="C34" s="4"/>
       <c r="D34" s="4"/>
       <c r="E34" s="4"/>

--- a/2026年上半年减肥记录每一天.xlsx
+++ b/2026年上半年减肥记录每一天.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="145" uniqueCount="89">
   <si>
     <t>时间</t>
   </si>
@@ -266,6 +266,46 @@
   </si>
   <si>
     <t>目前82.9kg
+本周争取到81.0kg</t>
+  </si>
+  <si>
+    <t>麻辣香锅</t>
+  </si>
+  <si>
+    <t>排骨 + 牛肉</t>
+  </si>
+  <si>
+    <t>一碗米饭</t>
+  </si>
+  <si>
+    <t>混合蔬菜</t>
+  </si>
+  <si>
+    <t>甜水饮料喝的多了点，注意</t>
+  </si>
+  <si>
+    <t>黄瓜鸡蛋汤 + 蒜蓉生菜 + 西兰花 + 麻辣香锅</t>
+  </si>
+  <si>
+    <t>生菜 + 西兰花</t>
+  </si>
+  <si>
+    <t>南瓜 + 鸡蛋</t>
+  </si>
+  <si>
+    <t>鸡蛋1个</t>
+  </si>
+  <si>
+    <t>南瓜</t>
+  </si>
+  <si>
+    <t>无</t>
+  </si>
+  <si>
+    <t>蔬菜少，需补充</t>
+  </si>
+  <si>
+    <t>目前82.55kg
 本周争取到81.0kg</t>
   </si>
 </sst>
@@ -1233,7 +1273,7 @@
   <cols>
     <col min="1" max="1" width="18.75" style="1" customWidth="1"/>
     <col min="2" max="2" width="14.5" style="1" customWidth="1"/>
-    <col min="3" max="3" width="43" style="1" customWidth="1"/>
+    <col min="3" max="3" width="49.25" style="1" customWidth="1"/>
     <col min="4" max="4" width="27.875" style="1" customWidth="1"/>
     <col min="5" max="5" width="20.875" style="1" customWidth="1"/>
     <col min="6" max="6" width="20.375" style="1" customWidth="1"/>
@@ -1821,9 +1861,6 @@
       <c r="C32" s="4" t="s">
         <v>73</v>
       </c>
-      <c r="D32" s="1"/>
-      <c r="E32" s="1"/>
-      <c r="F32" s="1"/>
       <c r="G32" s="4" t="s">
         <v>74</v>
       </c>
@@ -1836,11 +1873,21 @@
       <c r="B33" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="C33" s="4"/>
-      <c r="D33" s="4"/>
-      <c r="E33" s="4"/>
-      <c r="F33" s="4"/>
-      <c r="G33" s="4"/>
+      <c r="C33" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="D33" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="E33" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="F33" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="G33" s="4" t="s">
+        <v>80</v>
+      </c>
       <c r="H33" s="4"/>
     </row>
     <row r="34" spans="1:8">
@@ -1848,26 +1895,50 @@
       <c r="B34" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="C34" s="4"/>
+      <c r="C34" s="4" t="s">
+        <v>81</v>
+      </c>
       <c r="D34" s="4"/>
-      <c r="E34" s="4"/>
-      <c r="F34" s="4"/>
+      <c r="E34" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="F34" s="4" t="s">
+        <v>82</v>
+      </c>
       <c r="G34" s="4"/>
       <c r="H34" s="4"/>
     </row>
     <row r="35" spans="1:8">
-      <c r="A35" s="3"/>
-      <c r="B35" s="4"/>
-      <c r="C35" s="4"/>
-      <c r="D35" s="4"/>
-      <c r="E35" s="4"/>
-      <c r="F35" s="4"/>
-      <c r="G35" s="4"/>
-      <c r="H35" s="4"/>
+      <c r="A35" s="6">
+        <v>46210</v>
+      </c>
+      <c r="B35" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="C35" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="D35" s="4" t="s">
+        <v>84</v>
+      </c>
+      <c r="E35" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="F35" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="G35" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="H35" s="5" t="s">
+        <v>88</v>
+      </c>
     </row>
     <row r="36" spans="1:8">
-      <c r="A36" s="4"/>
-      <c r="B36" s="4"/>
+      <c r="A36" s="3"/>
+      <c r="B36" s="4" t="s">
+        <v>15</v>
+      </c>
       <c r="C36" s="4"/>
       <c r="D36" s="4"/>
       <c r="E36" s="4"/>
@@ -1876,8 +1947,10 @@
       <c r="H36" s="4"/>
     </row>
     <row r="37" spans="1:8">
-      <c r="A37" s="4"/>
-      <c r="B37" s="4"/>
+      <c r="A37" s="3"/>
+      <c r="B37" s="4" t="s">
+        <v>17</v>
+      </c>
       <c r="C37" s="4"/>
       <c r="D37" s="4"/>
       <c r="E37" s="4"/>
@@ -1886,17 +1959,17 @@
       <c r="H37" s="4"/>
     </row>
     <row r="38" spans="1:8">
-      <c r="A38" s="3"/>
+      <c r="A38" s="6"/>
       <c r="B38" s="4"/>
       <c r="C38" s="4"/>
-      <c r="D38" s="4"/>
-      <c r="E38" s="4"/>
-      <c r="F38" s="4"/>
+      <c r="D38" s="1"/>
+      <c r="E38" s="1"/>
+      <c r="F38" s="1"/>
       <c r="G38" s="4"/>
       <c r="H38" s="5"/>
     </row>
     <row r="39" spans="1:8">
-      <c r="A39" s="4"/>
+      <c r="A39" s="3"/>
       <c r="B39" s="4"/>
       <c r="C39" s="4"/>
       <c r="D39" s="4"/>
@@ -1906,7 +1979,7 @@
       <c r="H39" s="4"/>
     </row>
     <row r="40" spans="1:8">
-      <c r="A40" s="4"/>
+      <c r="A40" s="3"/>
       <c r="B40" s="4"/>
       <c r="C40" s="4"/>
       <c r="D40" s="4"/>

--- a/2026年上半年减肥记录每一天.xlsx
+++ b/2026年上半年减肥记录每一天.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="145" uniqueCount="89">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="151" uniqueCount="92">
   <si>
     <t>时间</t>
   </si>
@@ -306,6 +306,16 @@
   </si>
   <si>
     <t>目前82.55kg
+本周争取到81.0kg</t>
+  </si>
+  <si>
+    <t>鱼香肉丝 + 水煮菜 + 米饭</t>
+  </si>
+  <si>
+    <t>鸡腿 + 鸡蛋 + 全麦卷饼</t>
+  </si>
+  <si>
+    <t>目前82.1kg
 本周争取到81.0kg</t>
   </si>
 </sst>
@@ -1939,7 +1949,9 @@
       <c r="B36" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="C36" s="4"/>
+      <c r="C36" s="4" t="s">
+        <v>89</v>
+      </c>
       <c r="D36" s="4"/>
       <c r="E36" s="4"/>
       <c r="F36" s="4"/>
@@ -1959,18 +1971,28 @@
       <c r="H37" s="4"/>
     </row>
     <row r="38" spans="1:8">
-      <c r="A38" s="6"/>
-      <c r="B38" s="4"/>
-      <c r="C38" s="4"/>
-      <c r="D38" s="1"/>
-      <c r="E38" s="1"/>
-      <c r="F38" s="1"/>
+      <c r="A38" s="6">
+        <v>46210</v>
+      </c>
+      <c r="B38" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="C38" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="D38" s="4"/>
+      <c r="E38" s="4"/>
+      <c r="F38" s="4"/>
       <c r="G38" s="4"/>
-      <c r="H38" s="5"/>
+      <c r="H38" s="5" t="s">
+        <v>91</v>
+      </c>
     </row>
     <row r="39" spans="1:8">
       <c r="A39" s="3"/>
-      <c r="B39" s="4"/>
+      <c r="B39" s="4" t="s">
+        <v>15</v>
+      </c>
       <c r="C39" s="4"/>
       <c r="D39" s="4"/>
       <c r="E39" s="4"/>
@@ -1980,7 +2002,9 @@
     </row>
     <row r="40" spans="1:8">
       <c r="A40" s="3"/>
-      <c r="B40" s="4"/>
+      <c r="B40" s="4" t="s">
+        <v>17</v>
+      </c>
       <c r="C40" s="4"/>
       <c r="D40" s="4"/>
       <c r="E40" s="4"/>

--- a/2026年上半年减肥记录每一天.xlsx
+++ b/2026年上半年减肥记录每一天.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="151" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="159" uniqueCount="95">
   <si>
     <t>时间</t>
   </si>
@@ -317,6 +317,15 @@
   <si>
     <t>目前82.1kg
 本周争取到81.0kg</t>
+  </si>
+  <si>
+    <t>蘸酱菜 + 牛肉豌豆 + 米饭 + 全麦卷饼</t>
+  </si>
+  <si>
+    <t>鸡蛋饼</t>
+  </si>
+  <si>
+    <t>缺少蔬菜</t>
   </si>
 </sst>
 </file>
@@ -1972,7 +1981,7 @@
     </row>
     <row r="38" spans="1:8">
       <c r="A38" s="6">
-        <v>46210</v>
+        <v>46211</v>
       </c>
       <c r="B38" s="4" t="s">
         <v>8</v>
@@ -1993,7 +2002,9 @@
       <c r="B39" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="C39" s="4"/>
+      <c r="C39" s="4" t="s">
+        <v>56</v>
+      </c>
       <c r="D39" s="4"/>
       <c r="E39" s="4"/>
       <c r="F39" s="4"/>
@@ -2005,7 +2016,9 @@
       <c r="B40" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="C40" s="4"/>
+      <c r="C40" s="4" t="s">
+        <v>92</v>
+      </c>
       <c r="D40" s="4"/>
       <c r="E40" s="4"/>
       <c r="F40" s="4"/>
@@ -2013,18 +2026,30 @@
       <c r="H40" s="4"/>
     </row>
     <row r="41" spans="1:8">
-      <c r="A41" s="3"/>
-      <c r="B41" s="4"/>
-      <c r="C41" s="5"/>
+      <c r="A41" s="6">
+        <v>46212</v>
+      </c>
+      <c r="B41" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="C41" s="4" t="s">
+        <v>93</v>
+      </c>
       <c r="D41" s="4"/>
       <c r="E41" s="4"/>
       <c r="F41" s="4"/>
-      <c r="G41" s="4"/>
-      <c r="H41" s="4"/>
+      <c r="G41" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="H41" s="5" t="s">
+        <v>91</v>
+      </c>
     </row>
     <row r="42" spans="1:8">
-      <c r="A42" s="4"/>
-      <c r="B42" s="4"/>
+      <c r="A42" s="3"/>
+      <c r="B42" s="4" t="s">
+        <v>15</v>
+      </c>
       <c r="C42" s="4"/>
       <c r="D42" s="4"/>
       <c r="E42" s="4"/>
@@ -2033,8 +2058,10 @@
       <c r="H42" s="4"/>
     </row>
     <row r="43" spans="1:8">
-      <c r="A43" s="4"/>
-      <c r="B43" s="4"/>
+      <c r="A43" s="3"/>
+      <c r="B43" s="4" t="s">
+        <v>17</v>
+      </c>
       <c r="C43" s="4"/>
       <c r="D43" s="4"/>
       <c r="E43" s="4"/>

--- a/2026年上半年减肥记录每一天.xlsx
+++ b/2026年上半年减肥记录每一天.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="159" uniqueCount="95">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="168" uniqueCount="98">
   <si>
     <t>时间</t>
   </si>
@@ -326,6 +326,16 @@
   </si>
   <si>
     <t>缺少蔬菜</t>
+  </si>
+  <si>
+    <t>鸡蛋1 + 2小块玉米 + 西红柿1</t>
+  </si>
+  <si>
+    <t>2小块玉米</t>
+  </si>
+  <si>
+    <t>目前82.05kg
+本周争取到81.0kg</t>
   </si>
 </sst>
 </file>
@@ -2070,18 +2080,36 @@
       <c r="H43" s="4"/>
     </row>
     <row r="44" spans="1:8">
-      <c r="A44" s="3"/>
-      <c r="B44" s="4"/>
-      <c r="C44" s="4"/>
-      <c r="D44" s="4"/>
-      <c r="E44" s="4"/>
-      <c r="F44" s="4"/>
-      <c r="G44" s="4"/>
-      <c r="H44" s="4"/>
+      <c r="A44" s="6">
+        <v>46226</v>
+      </c>
+      <c r="B44" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="C44" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="D44" s="4" t="s">
+        <v>84</v>
+      </c>
+      <c r="E44" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="F44" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="G44" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="H44" s="5" t="s">
+        <v>97</v>
+      </c>
     </row>
     <row r="45" spans="1:8">
-      <c r="A45" s="4"/>
-      <c r="B45" s="4"/>
+      <c r="A45" s="3"/>
+      <c r="B45" s="4" t="s">
+        <v>15</v>
+      </c>
       <c r="C45" s="4"/>
       <c r="D45" s="4"/>
       <c r="E45" s="4"/>
@@ -2090,8 +2118,10 @@
       <c r="H45" s="4"/>
     </row>
     <row r="46" spans="1:8">
-      <c r="A46" s="4"/>
-      <c r="B46" s="4"/>
+      <c r="A46" s="3"/>
+      <c r="B46" s="4" t="s">
+        <v>17</v>
+      </c>
       <c r="C46" s="4"/>
       <c r="D46" s="4"/>
       <c r="E46" s="4"/>

--- a/2026年上半年减肥记录每一天.xlsx
+++ b/2026年上半年减肥记录每一天.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="168" uniqueCount="98">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="191" uniqueCount="109">
   <si>
     <t>时间</t>
   </si>
@@ -336,6 +336,41 @@
   <si>
     <t>目前82.05kg
 本周争取到81.0kg</t>
+  </si>
+  <si>
+    <t>缺少主食和蛋白质</t>
+  </si>
+  <si>
+    <t>目前84.8kg
+本周争取到83.0kg</t>
+  </si>
+  <si>
+    <t>土豆2</t>
+  </si>
+  <si>
+    <t>盐水鸭 + 西红柿炒鸡蛋 + 米饭</t>
+  </si>
+  <si>
+    <t>板烧汉堡 + 豆浆 + 油条</t>
+  </si>
+  <si>
+    <t>板烧鸡腿肉</t>
+  </si>
+  <si>
+    <t>很少生菜</t>
+  </si>
+  <si>
+    <t>比较满意，生活化</t>
+  </si>
+  <si>
+    <t>目前83.7kg
+本周争取到83.0kg</t>
+  </si>
+  <si>
+    <t>乡村基</t>
+  </si>
+  <si>
+    <t>比较满意</t>
   </si>
 </sst>
 </file>
@@ -2130,29 +2165,57 @@
       <c r="H46" s="4"/>
     </row>
     <row r="47" spans="1:8">
-      <c r="A47" s="3"/>
-      <c r="B47" s="4"/>
-      <c r="C47" s="4"/>
+      <c r="A47" s="6">
+        <v>46233</v>
+      </c>
+      <c r="B47" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="C47" s="4" t="s">
+        <v>19</v>
+      </c>
       <c r="D47" s="4"/>
       <c r="E47" s="4"/>
-      <c r="F47" s="4"/>
-      <c r="G47" s="4"/>
-      <c r="H47" s="4"/>
+      <c r="F47" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="G47" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="H47" s="5" t="s">
+        <v>99</v>
+      </c>
     </row>
     <row r="48" spans="1:8">
-      <c r="A48" s="4"/>
-      <c r="B48" s="4"/>
-      <c r="C48" s="4"/>
-      <c r="D48" s="4"/>
-      <c r="E48" s="4"/>
-      <c r="F48" s="4"/>
-      <c r="G48" s="4"/>
+      <c r="A48" s="3"/>
+      <c r="B48" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="C48" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="D48" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="E48" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="F48" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="G48" s="4" t="s">
+        <v>6</v>
+      </c>
       <c r="H48" s="4"/>
     </row>
     <row r="49" spans="1:8">
-      <c r="A49" s="4"/>
-      <c r="B49" s="4"/>
-      <c r="C49" s="4"/>
+      <c r="A49" s="3"/>
+      <c r="B49" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="C49" s="4" t="s">
+        <v>101</v>
+      </c>
       <c r="D49" s="4"/>
       <c r="E49" s="4"/>
       <c r="F49" s="4"/>
@@ -2160,31 +2223,56 @@
       <c r="H49" s="4"/>
     </row>
     <row r="50" spans="1:8">
-      <c r="A50" s="3"/>
-      <c r="B50" s="4"/>
-      <c r="C50" s="4"/>
-      <c r="D50" s="4"/>
+      <c r="A50" s="6">
+        <v>46234</v>
+      </c>
+      <c r="B50" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="C50" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="D50" s="4" t="s">
+        <v>103</v>
+      </c>
       <c r="E50" s="4"/>
-      <c r="F50" s="4"/>
-      <c r="G50" s="4"/>
+      <c r="F50" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="G50" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="H50" s="5" t="s">
+        <v>106</v>
+      </c>
     </row>
     <row r="51" spans="1:8">
-      <c r="A51" s="4"/>
-      <c r="B51" s="4"/>
-      <c r="C51" s="4"/>
+      <c r="A51" s="3"/>
+      <c r="B51" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="C51" s="4" t="s">
+        <v>107</v>
+      </c>
       <c r="D51" s="4"/>
       <c r="E51" s="4"/>
       <c r="F51" s="4"/>
-      <c r="G51" s="4"/>
+      <c r="G51" s="4" t="s">
+        <v>108</v>
+      </c>
+      <c r="H51" s="4"/>
     </row>
     <row r="52" spans="1:8">
-      <c r="A52" s="4"/>
-      <c r="B52" s="4"/>
+      <c r="A52" s="3"/>
+      <c r="B52" s="4" t="s">
+        <v>17</v>
+      </c>
       <c r="C52" s="4"/>
       <c r="D52" s="4"/>
       <c r="E52" s="4"/>
       <c r="F52" s="4"/>
       <c r="G52" s="4"/>
+      <c r="H52" s="4"/>
     </row>
     <row r="53" spans="1:8">
       <c r="A53" s="3"/>
@@ -4019,7 +4107,7 @@
       <c r="H236" s="5"/>
     </row>
   </sheetData>
-  <mergeCells count="154">
+  <mergeCells count="155">
     <mergeCell ref="A2:A4"/>
     <mergeCell ref="A5:A7"/>
     <mergeCell ref="A8:A10"/>
@@ -4114,6 +4202,7 @@
     <mergeCell ref="H41:H43"/>
     <mergeCell ref="H44:H46"/>
     <mergeCell ref="H47:H49"/>
+    <mergeCell ref="H50:H52"/>
     <mergeCell ref="H56:H58"/>
     <mergeCell ref="H59:H61"/>
     <mergeCell ref="H62:H64"/>

--- a/2026年上半年减肥记录每一天.xlsx
+++ b/2026年上半年减肥记录每一天.xlsx
@@ -1,8 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\cloud_security_study_public\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
     <workbookView windowWidth="31545" windowHeight="17655"/>
   </bookViews>
@@ -29,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="191" uniqueCount="109">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="197" uniqueCount="112">
   <si>
     <t>时间</t>
   </si>
@@ -371,6 +376,16 @@
   </si>
   <si>
     <t>比较满意</t>
+  </si>
+  <si>
+    <t>一个红糖包子</t>
+  </si>
+  <si>
+    <t>缺少蔬菜和蛋白质</t>
+  </si>
+  <si>
+    <t>目前83.3kg
+本周争取到82.0kg</t>
   </si>
 </sst>
 </file>
@@ -2275,31 +2290,48 @@
       <c r="H52" s="4"/>
     </row>
     <row r="53" spans="1:8">
-      <c r="A53" s="3"/>
-      <c r="B53" s="4"/>
-      <c r="C53" s="4"/>
+      <c r="A53" s="6">
+        <v>46239</v>
+      </c>
+      <c r="B53" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="C53" s="4" t="s">
+        <v>109</v>
+      </c>
       <c r="D53" s="4"/>
       <c r="E53" s="4"/>
       <c r="F53" s="4"/>
-      <c r="G53" s="4"/>
+      <c r="G53" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="H53" s="5" t="s">
+        <v>111</v>
+      </c>
     </row>
     <row r="54" spans="1:8">
-      <c r="A54" s="4"/>
-      <c r="B54" s="4"/>
+      <c r="A54" s="3"/>
+      <c r="B54" s="4" t="s">
+        <v>15</v>
+      </c>
       <c r="C54" s="4"/>
       <c r="D54" s="4"/>
       <c r="E54" s="4"/>
       <c r="F54" s="4"/>
       <c r="G54" s="4"/>
+      <c r="H54" s="4"/>
     </row>
     <row r="55" spans="1:8">
-      <c r="A55" s="4"/>
-      <c r="B55" s="4"/>
+      <c r="A55" s="3"/>
+      <c r="B55" s="4" t="s">
+        <v>17</v>
+      </c>
       <c r="C55" s="4"/>
       <c r="D55" s="4"/>
       <c r="E55" s="4"/>
       <c r="F55" s="4"/>
       <c r="G55" s="4"/>
+      <c r="H55" s="4"/>
     </row>
     <row r="56" spans="1:8">
       <c r="A56" s="3"/>
@@ -4107,7 +4139,7 @@
       <c r="H236" s="5"/>
     </row>
   </sheetData>
-  <mergeCells count="155">
+  <mergeCells count="156">
     <mergeCell ref="A2:A4"/>
     <mergeCell ref="A5:A7"/>
     <mergeCell ref="A8:A10"/>
@@ -4203,6 +4235,7 @@
     <mergeCell ref="H44:H46"/>
     <mergeCell ref="H47:H49"/>
     <mergeCell ref="H50:H52"/>
+    <mergeCell ref="H53:H55"/>
     <mergeCell ref="H56:H58"/>
     <mergeCell ref="H59:H61"/>
     <mergeCell ref="H62:H64"/>

--- a/2026年上半年减肥记录每一天.xlsx
+++ b/2026年上半年减肥记录每一天.xlsx
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="197" uniqueCount="112">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="206" uniqueCount="115">
   <si>
     <t>时间</t>
   </si>
@@ -378,14 +378,24 @@
     <t>比较满意</t>
   </si>
   <si>
-    <t>一个红糖包子</t>
-  </si>
-  <si>
-    <t>缺少蔬菜和蛋白质</t>
-  </si>
-  <si>
-    <t>目前83.3kg
-本周争取到82.0kg</t>
+    <t>2026-8-13 周四</t>
+  </si>
+  <si>
+    <t>鸡蛋2个 + 西红柿1</t>
+  </si>
+  <si>
+    <t>鸡蛋2个</t>
+  </si>
+  <si>
+    <t>目前83.5kg
+本周争取到83.0kg</t>
+  </si>
+  <si>
+    <t>2026-8-13 周五</t>
+  </si>
+  <si>
+    <t>目前kg
+本周争取到83.0kg</t>
   </si>
 </sst>
 </file>
@@ -2290,23 +2300,29 @@
       <c r="H52" s="4"/>
     </row>
     <row r="53" spans="1:8">
-      <c r="A53" s="6">
-        <v>46239</v>
+      <c r="A53" s="6" t="s">
+        <v>109</v>
       </c>
       <c r="B53" s="4" t="s">
         <v>8</v>
       </c>
       <c r="C53" s="4" t="s">
-        <v>109</v>
-      </c>
-      <c r="D53" s="4"/>
-      <c r="E53" s="4"/>
-      <c r="F53" s="4"/>
+        <v>110</v>
+      </c>
+      <c r="D53" s="4" t="s">
+        <v>111</v>
+      </c>
+      <c r="E53" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="F53" s="4" t="s">
+        <v>19</v>
+      </c>
       <c r="G53" s="4" t="s">
-        <v>110</v>
+        <v>6</v>
       </c>
       <c r="H53" s="5" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
     </row>
     <row r="54" spans="1:8">
@@ -2334,18 +2350,26 @@
       <c r="H55" s="4"/>
     </row>
     <row r="56" spans="1:8">
-      <c r="A56" s="3"/>
-      <c r="B56" s="4"/>
+      <c r="A56" s="6" t="s">
+        <v>113</v>
+      </c>
+      <c r="B56" s="4" t="s">
+        <v>8</v>
+      </c>
       <c r="C56" s="4"/>
       <c r="D56" s="4"/>
       <c r="E56" s="4"/>
       <c r="F56" s="4"/>
       <c r="G56" s="4"/>
-      <c r="H56" s="4"/>
+      <c r="H56" s="5" t="s">
+        <v>114</v>
+      </c>
     </row>
     <row r="57" spans="1:8">
-      <c r="A57" s="4"/>
-      <c r="B57" s="4"/>
+      <c r="A57" s="3"/>
+      <c r="B57" s="4" t="s">
+        <v>15</v>
+      </c>
       <c r="C57" s="4"/>
       <c r="D57" s="4"/>
       <c r="E57" s="4"/>
@@ -2354,8 +2378,10 @@
       <c r="H57" s="4"/>
     </row>
     <row r="58" spans="1:8">
-      <c r="A58" s="4"/>
-      <c r="B58" s="4"/>
+      <c r="A58" s="3"/>
+      <c r="B58" s="4" t="s">
+        <v>17</v>
+      </c>
       <c r="C58" s="4"/>
       <c r="D58" s="4"/>
       <c r="E58" s="4"/>

--- a/2026年上半年减肥记录每一天.xlsx
+++ b/2026年上半年减肥记录每一天.xlsx
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="206" uniqueCount="115">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="226" uniqueCount="124">
   <si>
     <t>时间</t>
   </si>
@@ -391,11 +391,38 @@
 本周争取到83.0kg</t>
   </si>
   <si>
+    <t>鸡腿1 + 鸡蛋1</t>
+  </si>
+  <si>
+    <t>西红柿鸡蛋 + 白菜豆腐 + 大米饭</t>
+  </si>
+  <si>
+    <t>鸡蛋 + 豆腐</t>
+  </si>
+  <si>
+    <t>大米饭</t>
+  </si>
+  <si>
+    <t>西红柿 + 白菜</t>
+  </si>
+  <si>
+    <t>比较满意，生活化，米饭有点多</t>
+  </si>
+  <si>
     <t>2026-8-13 周五</t>
   </si>
   <si>
-    <t>目前kg
-本周争取到83.0kg</t>
+    <t>西红柿1 + 溏心蛋2</t>
+  </si>
+  <si>
+    <t>溏心蛋2</t>
+  </si>
+  <si>
+    <t>缺少主食如玉米</t>
+  </si>
+  <si>
+    <t>目前82.95kg
+本周争取到82.5kg</t>
   </si>
 </sst>
 </file>
@@ -2330,11 +2357,21 @@
       <c r="B54" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="C54" s="4"/>
-      <c r="D54" s="4"/>
-      <c r="E54" s="4"/>
-      <c r="F54" s="4"/>
-      <c r="G54" s="4"/>
+      <c r="C54" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="D54" s="4" t="s">
+        <v>113</v>
+      </c>
+      <c r="E54" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="F54" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="G54" s="4" t="s">
+        <v>6</v>
+      </c>
       <c r="H54" s="4"/>
     </row>
     <row r="55" spans="1:8">
@@ -2342,27 +2379,47 @@
       <c r="B55" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="C55" s="4"/>
-      <c r="D55" s="4"/>
-      <c r="E55" s="4"/>
-      <c r="F55" s="4"/>
-      <c r="G55" s="4"/>
+      <c r="C55" s="4" t="s">
+        <v>114</v>
+      </c>
+      <c r="D55" s="4" t="s">
+        <v>115</v>
+      </c>
+      <c r="E55" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="F55" s="4" t="s">
+        <v>117</v>
+      </c>
+      <c r="G55" s="4" t="s">
+        <v>118</v>
+      </c>
       <c r="H55" s="4"/>
     </row>
     <row r="56" spans="1:8">
       <c r="A56" s="6" t="s">
-        <v>113</v>
+        <v>119</v>
       </c>
       <c r="B56" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="C56" s="4"/>
-      <c r="D56" s="4"/>
-      <c r="E56" s="4"/>
-      <c r="F56" s="4"/>
-      <c r="G56" s="4"/>
+      <c r="C56" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="D56" s="4" t="s">
+        <v>121</v>
+      </c>
+      <c r="E56" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="F56" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="G56" s="4" t="s">
+        <v>122</v>
+      </c>
       <c r="H56" s="5" t="s">
-        <v>114</v>
+        <v>123</v>
       </c>
     </row>
     <row r="57" spans="1:8">
@@ -2370,11 +2427,21 @@
       <c r="B57" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="C57" s="4"/>
-      <c r="D57" s="4"/>
-      <c r="E57" s="4"/>
-      <c r="F57" s="4"/>
-      <c r="G57" s="4"/>
+      <c r="C57" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="D57" s="4" t="s">
+        <v>113</v>
+      </c>
+      <c r="E57" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="F57" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="G57" s="4" t="s">
+        <v>6</v>
+      </c>
       <c r="H57" s="4"/>
     </row>
     <row r="58" spans="1:8">
